--- a/grupos/4APM - Estadisticos 20212.xlsx
+++ b/grupos/4APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -158,18 +158,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -188,6 +188,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -197,9 +206,6 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>CUEVAS</t>
   </si>
   <si>
@@ -257,9 +263,6 @@
     <t>ZAVALETA</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
@@ -315,9 +318,6 @@
   </si>
   <si>
     <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
   </si>
   <si>
     <t>CESAR</t>
@@ -885,7 +885,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -948,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1063,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         <v>-1</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1241,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1304,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1419,7 +1419,7 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1508,7 +1508,7 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -1571,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1597,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1686,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1749,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1775,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1864,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -1927,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>9</v>
@@ -2016,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>9</v>
@@ -2042,7 +2042,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>7</v>
@@ -2105,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2131,7 +2131,7 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>8</v>
@@ -2194,7 +2194,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2220,7 +2220,7 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>9</v>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2309,7 +2309,7 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2372,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2398,7 +2398,7 @@
         <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2461,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2487,7 +2487,7 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2576,7 +2576,7 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2665,7 +2665,7 @@
         <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2728,7 +2728,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2754,7 +2754,7 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2843,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>9</v>
@@ -2906,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2932,7 +2932,7 @@
         <v>7</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>9</v>
@@ -2995,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -3063,27 +3063,30 @@
         <v>24</v>
       </c>
       <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>66.67</v>
+      </c>
+      <c r="G2">
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>24</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -3095,27 +3098,27 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>66.67</v>
       </c>
       <c r="G3">
-        <v>33.33</v>
+        <v>29.17</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -3124,30 +3127,30 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="G4">
         <v>29.17</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -3156,19 +3159,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>70.83</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>29.17</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3280,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3309,62 +3312,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920336</v>
+        <v>20330051920339</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920337</v>
+        <v>20330051920339</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920263</v>
+        <v>20330051920339</v>
       </c>
       <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3372,499 +3375,19 @@
         <v>20330051920339</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920339</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920339</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920339</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920339</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920340</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920341</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920342</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920344</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920345</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920381</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920346</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920347</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920348</v>
-      </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920349</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920350</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920352</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920353</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920354</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920355</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920382</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330050470596</v>
-      </c>
-      <c r="B26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920356</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920357</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920383</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3903,16 +3426,16 @@
         <v>20330051920339</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3920,16 +3443,16 @@
         <v>20330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3937,16 +3460,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3954,16 +3477,16 @@
         <v>20330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3971,16 +3494,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
         <v>100</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3988,16 +3511,16 @@
         <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>101</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4005,16 +3528,16 @@
         <v>20330051920342</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>102</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4022,16 +3545,16 @@
         <v>20330051920344</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>103</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4039,16 +3562,16 @@
         <v>20330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>104</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4056,16 +3579,16 @@
         <v>20330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
         <v>105</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4073,16 +3596,16 @@
         <v>20330051920346</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>106</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4090,16 +3613,16 @@
         <v>20330051920347</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>107</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4107,16 +3630,16 @@
         <v>20330051920348</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>106</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4124,16 +3647,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4141,16 +3664,16 @@
         <v>20330051920350</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4158,16 +3681,16 @@
         <v>20330051920352</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4175,16 +3698,16 @@
         <v>20330051920353</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4192,16 +3715,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4209,16 +3732,16 @@
         <v>20330051920355</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4226,16 +3749,16 @@
         <v>20330051920382</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>102</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4243,16 +3766,16 @@
         <v>19330050470596</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
         <v>113</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4260,16 +3783,16 @@
         <v>20330051920356</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
         <v>114</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4277,16 +3800,16 @@
         <v>20330051920357</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4294,16 +3817,16 @@
         <v>20330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>116</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4345,22 +3868,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920382</v>
+        <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4368,324 +3891,209 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920382</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>46</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920342</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920263</v>
+        <v>20330051920345</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920344</v>
+        <v>20330051920345</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>46</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920348</v>
+        <v>20330051920382</v>
       </c>
       <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920349</v>
+        <v>19330050470596</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920350</v>
+        <v>19330050470596</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920352</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920353</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920355</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920357</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920383</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4APM - Estadisticos 20212.xlsx
+++ b/grupos/4APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -161,10 +161,10 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Medina Tolentino Elio</t>
@@ -894,13 +894,13 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -909,7 +909,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -942,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>9</v>
@@ -983,13 +983,13 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -998,7 +998,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1072,13 +1072,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1120,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>9</v>
@@ -1129,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1176,7 +1176,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1250,13 +1250,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1339,7 +1339,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1354,7 +1354,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1428,13 +1428,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1443,7 +1443,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1517,13 +1517,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1532,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1574,7 +1574,7 @@
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1606,13 +1606,13 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1621,7 +1621,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1648,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1695,13 +1695,13 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1710,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1743,7 +1743,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -1752,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1784,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1799,7 +1799,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1873,13 +1873,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1962,13 +1962,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1977,7 +1977,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2010,7 +2010,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2019,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2051,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2066,7 +2066,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2140,13 +2140,13 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2155,7 +2155,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2188,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2229,13 +2229,13 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2244,7 +2244,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2286,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2318,7 +2318,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2333,7 +2333,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2407,13 +2407,13 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2422,7 +2422,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2496,13 +2496,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2511,7 +2511,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2553,7 +2553,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2585,13 +2585,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2600,7 +2600,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2674,13 +2674,13 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2689,7 +2689,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -2763,13 +2763,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2778,7 +2778,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2852,13 +2852,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2867,7 +2867,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2900,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -2941,7 +2941,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2956,7 +2956,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2998,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3063,16 +3063,16 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>29.17</v>
       </c>
       <c r="H2">
         <v>6.8</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -3095,30 +3095,30 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>29.17</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -3127,25 +3127,25 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>29.17</v>
+        <v>20.83</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3367,7 +3367,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3836,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3883,7 +3883,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3952,7 +3952,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3960,22 +3960,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3983,22 +3983,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920382</v>
+        <v>20330051920354</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4029,22 +4029,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920382</v>
+        <v>20330051920354</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4052,22 +4052,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330050470596</v>
+        <v>20330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4075,24 +4075,93 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>20330051920382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>19330050470596</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>74</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>94</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>113</v>
       </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330050470596</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
         <v>50</v>
       </c>
-      <c r="G11">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920345</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20212.xlsx
+++ b/grupos/4APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -158,6 +158,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -165,9 +168,6 @@
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -891,7 +891,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -903,10 +903,10 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -948,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -980,22 +980,22 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1034,10 +1034,10 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1069,22 +1069,22 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1149,7 +1149,7 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1170,10 +1170,10 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1212,7 +1212,7 @@
         <v>-1</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1259,10 +1259,10 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1301,10 +1301,10 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1336,22 +1336,22 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1437,10 +1437,10 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1467,7 +1467,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1479,10 +1479,10 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1514,22 +1514,22 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1615,10 +1615,10 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1692,22 +1692,22 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1746,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1793,10 +1793,10 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -1876,16 +1876,16 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1927,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1959,22 +1959,22 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2016,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2057,13 +2057,13 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -2105,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2137,22 +2137,22 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -2179,7 +2179,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2194,7 +2194,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2226,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2268,7 +2268,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2280,10 +2280,10 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2327,10 +2327,10 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2372,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2416,10 +2416,10 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2461,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2493,22 +2493,22 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2535,7 +2535,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2547,10 +2547,10 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2582,22 +2582,22 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2624,13 +2624,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2671,22 +2671,22 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2713,7 +2713,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2728,7 +2728,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2772,10 +2772,10 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2814,10 +2814,10 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2849,22 +2849,22 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2906,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2938,22 +2938,22 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2995,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -3063,19 +3063,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>70.83</v>
+        <v>33.33</v>
       </c>
       <c r="G2">
-        <v>29.17</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -3095,19 +3095,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>29.17</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -3130,27 +3130,27 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>75</v>
       </c>
       <c r="G4">
-        <v>20.83</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -3159,25 +3159,25 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>20.83</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3255,25 +3255,25 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>91.67</v>
+      </c>
+      <c r="G8">
+        <v>8.33</v>
+      </c>
+      <c r="H8">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>95.83</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>8.4</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>4.17</v>
       </c>
     </row>
   </sheetData>
@@ -3283,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3324,10 +3324,10 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3344,10 +3344,10 @@
         <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3364,29 +3364,9 @@
         <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920339</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3435,7 +3415,7 @@
         <v>58</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3836,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3868,19 +3848,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920340</v>
+        <v>20330051920381</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>48</v>
@@ -3891,19 +3871,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920381</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>46</v>
@@ -3914,22 +3894,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920342</v>
+        <v>20330051920354</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3937,22 +3917,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920342</v>
+        <v>20330051920354</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3960,22 +3940,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920381</v>
+        <v>20330051920382</v>
       </c>
       <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
         <v>64</v>
       </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3983,22 +3963,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920381</v>
+        <v>20330051920382</v>
       </c>
       <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4006,22 +3986,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920354</v>
+        <v>19330050470596</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4029,22 +4009,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920354</v>
+        <v>19330050470596</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4052,22 +4032,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920382</v>
+        <v>20330051920337</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4075,22 +4055,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920382</v>
+        <v>20330051920344</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4098,19 +4078,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330050470596</v>
+        <v>20330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -4121,22 +4101,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330050470596</v>
+        <v>20330051920347</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4144,24 +4124,116 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920345</v>
+        <v>20330051920349</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>46</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920350</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920352</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920357</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920383</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20212.xlsx
+++ b/grupos/4APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -158,22 +158,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>NC</t>
@@ -897,7 +897,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -915,7 +915,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -924,13 +924,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -945,10 +945,10 @@
         <v>7</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1004,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1013,13 +1013,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1034,10 +1034,10 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1084,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -1093,7 +1093,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1102,13 +1102,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1137,13 +1137,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1182,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1191,22 +1191,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1247,13 +1247,13 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1271,7 +1271,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1280,19 +1280,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>5</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1301,10 +1301,10 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1360,7 +1360,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1369,13 +1369,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1393,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1431,7 +1431,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1440,7 +1440,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1449,7 +1449,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1458,13 +1458,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1479,13 +1479,13 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1529,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1538,7 +1538,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1547,13 +1547,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1571,10 +1571,10 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1603,13 +1603,13 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1618,7 +1618,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1627,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1636,13 +1636,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1660,10 +1660,10 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1707,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1716,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1725,19 +1725,19 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1746,13 +1746,13 @@
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1781,13 +1781,13 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1796,7 +1796,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1805,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1814,22 +1814,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1885,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1894,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1903,16 +1903,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1924,10 +1924,10 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1974,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1983,7 +1983,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1992,13 +1992,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2016,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2081,13 +2081,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2105,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2152,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -2161,7 +2161,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2170,13 +2170,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2191,13 +2191,13 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2241,7 +2241,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2250,7 +2250,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2259,13 +2259,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2283,7 +2283,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2324,13 +2324,13 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>9</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2339,7 +2339,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2348,19 +2348,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2369,10 +2369,10 @@
         <v>6</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2404,13 +2404,13 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2428,7 +2428,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2437,19 +2437,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2458,13 +2458,13 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2508,7 +2508,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2526,19 +2526,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2547,13 +2547,13 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2597,7 +2597,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2615,19 +2615,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2639,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2686,7 +2686,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2695,7 +2695,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2704,19 +2704,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2725,10 +2725,10 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2760,13 +2760,13 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2784,7 +2784,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2793,22 +2793,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2817,10 +2817,10 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2864,7 +2864,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2873,7 +2873,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2882,13 +2882,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2906,10 +2906,10 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2947,13 +2947,13 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>6</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2962,7 +2962,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2971,19 +2971,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2995,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -3063,30 +3063,30 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>33.33</v>
+        <v>75</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>20.83</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -3095,19 +3095,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>70.83</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>29.17</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3118,28 +3118,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>24</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3150,71 +3150,71 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>24</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="G5">
-        <v>20.83</v>
+        <v>8.33</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>24</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -3223,30 +3223,30 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="G7">
         <v>8.33</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -3255,16 +3255,16 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>8.300000000000001</v>
@@ -3283,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3324,50 +3324,10 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920339</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920339</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3415,7 +3375,7 @@
         <v>58</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3816,7 +3776,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3848,22 +3808,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920381</v>
+        <v>20330051920341</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3871,19 +3831,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920381</v>
+        <v>20330051920341</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>46</v>
@@ -3894,22 +3854,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920354</v>
+        <v>20330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3917,22 +3877,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920354</v>
+        <v>20330051920342</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3940,22 +3900,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920382</v>
+        <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3963,22 +3923,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920382</v>
+        <v>19330050470596</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3986,254 +3946,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330050470596</v>
+        <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330050470596</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920337</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920344</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920345</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920347</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920349</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920350</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920352</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920357</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920383</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20212.xlsx
+++ b/grupos/4APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -158,21 +158,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
@@ -188,136 +188,136 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBANO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>ZAVALETA</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
     <t>GERARDO</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XILCAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
   </si>
   <si>
     <t>CESAR</t>
@@ -912,28 +912,28 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -942,13 +942,13 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -1001,34 +1001,34 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>7</v>
@@ -1090,22 +1090,22 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1146,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1158,7 +1158,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1167,7 +1167,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1179,22 +1179,22 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1209,13 +1209,13 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1268,28 +1268,28 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>7</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1345,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1357,28 +1357,28 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1387,7 +1387,7 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1446,22 +1446,22 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1476,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1535,37 +1535,37 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1624,22 +1624,22 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1713,22 +1713,22 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1740,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1749,7 +1749,7 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1790,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1802,22 +1802,22 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1891,22 +1891,22 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1918,7 +1918,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>7</v>
@@ -1980,22 +1980,22 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2010,7 +2010,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2048,13 +2048,13 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -2069,28 +2069,28 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>7</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2158,22 +2158,22 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2247,28 +2247,28 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2315,13 +2315,13 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2336,22 +2336,22 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2366,7 +2366,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2425,28 +2425,28 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2461,7 +2461,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2514,43 +2514,43 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -2603,22 +2603,22 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2692,34 +2692,34 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>7</v>
@@ -2728,7 +2728,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2781,37 +2781,37 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2870,22 +2870,22 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2959,22 +2959,22 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -3063,30 +3063,30 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="G2">
-        <v>20.83</v>
+        <v>8.33</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -3095,19 +3095,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3118,28 +3118,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>24</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>24</v>
@@ -3171,7 +3171,7 @@
         <v>8.33</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>24</v>
@@ -3203,7 +3203,7 @@
         <v>8.33</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -3235,7 +3235,7 @@
         <v>8.33</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3283,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3308,26 +3308,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920339</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3363,30 +3343,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920339</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>97</v>
@@ -3397,13 +3377,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920337</v>
+        <v>20330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>98</v>
@@ -3414,13 +3394,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920263</v>
+        <v>20330051920339</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -3434,10 +3414,10 @@
         <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>100</v>
@@ -3451,10 +3431,10 @@
         <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>101</v>
@@ -3468,10 +3448,10 @@
         <v>20330051920342</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
         <v>102</v>
@@ -3485,10 +3465,10 @@
         <v>20330051920344</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>103</v>
@@ -3502,10 +3482,10 @@
         <v>20330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>104</v>
@@ -3519,10 +3499,10 @@
         <v>20330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>105</v>
@@ -3536,10 +3516,10 @@
         <v>20330051920346</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
         <v>106</v>
@@ -3553,10 +3533,10 @@
         <v>20330051920347</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
         <v>107</v>
@@ -3570,10 +3550,10 @@
         <v>20330051920348</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>106</v>
@@ -3587,10 +3567,10 @@
         <v>20330051920349</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3604,10 +3584,10 @@
         <v>20330051920350</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3621,10 +3601,10 @@
         <v>20330051920352</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3638,10 +3618,10 @@
         <v>20330051920353</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3655,10 +3635,10 @@
         <v>20330051920354</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3672,10 +3652,10 @@
         <v>20330051920355</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
@@ -3689,10 +3669,10 @@
         <v>20330051920382</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>102</v>
@@ -3706,10 +3686,10 @@
         <v>19330050470596</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
         <v>113</v>
@@ -3723,10 +3703,10 @@
         <v>20330051920356</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>114</v>
@@ -3740,10 +3720,10 @@
         <v>20330051920357</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -3757,10 +3737,10 @@
         <v>20330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>116</v>
@@ -3776,7 +3756,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3806,167 +3786,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920341</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920341</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920342</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920342</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920340</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330050470596</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920356</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
